--- a/translators/translator_bmc_at_v2.0.0.xlsx
+++ b/translators/translator_bmc_at_v2.0.0.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -76,6 +76,21 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002B5B47"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000563C1"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -121,7 +136,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -144,6 +159,7 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -177,7 +193,7 @@
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -201,6 +217,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -461,96 +480,165 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="85" customWidth="1" style="6" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF – Open Building Data Format</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Version 2.0.0 | October 2026 | pre-validation</t>
-        </is>
-      </c>
-    </row>
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>OpenBDF - Open Building Data Format</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="4" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>OpenBDF is pre-existing intellectual property of the Global Building Data</t>
-        </is>
-      </c>
-    </row>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Version 2.0.0 | October 2026 | pre-release</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Initiative (GBDI) at EPFL. It remains the property of GBDI.</t>
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>OpenBDF is developed by the team of GBDI Global Building Data Initiative at EPFL</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n"/>
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>and RISE with technical support from EPFL ENAC-IT4R. This version is shared for</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>This version is shared for expert review ahead of the November 2026 workshops</t>
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>expert review and is not yet validated. Any licence to use it is non-exclusive</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>and is not yet validated. Any licence to use it is non-exclusive and limited to</t>
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>and limited to the purpose for which it was shared. While we welcome feedback</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>the purpose for which it was shared. Material changes to the specification are</t>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>and proposals to evolve the format, material changes to the specification are to</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>to be agreed with GBDI before they are made, so that the format is not split before it is consolidated.</t>
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>be agreed with GBDI before they are published, so that the format remains</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Author: Dr Eng. Nicole Di Santo, Technical Lead, GBDI, LMC, EPFL, Lausanne.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>coherent and adjustments can be consolidated ahead of releases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Parser and code implementation: ENAC-IT4R, EPFL, Lausanne</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Code repository: https://github.com/EPFL-ENAC/lmc-openbdf/ </t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Authors: Nicole Di Santo¹, Martin Röck²</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Contributors: Karen Scrivener¹, Vanderley John³, Zuhaib Batra¹</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1. GBDI Global Building Data Initiative, EPFL LMC, Lausanne, Switzerland</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2. RISE Institute for Regenerative Spatial Systems Science, Vienna, Austria</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3. University of São Paulo, São Paulo, Brazil</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Contacts:</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>nicole.disanto@epfl.ch</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>martin.roeck@riselabs.at</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Parser and code implementation with support of ENAC-IT4R, EPFL, Lausanne.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>GitHub repository:</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>https://github.com/EPFL-ENAC/lmc-openbdf/</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
